--- a/results-list/g1-comerro-1.xlsx
+++ b/results-list/g1-comerro-1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9D0128C-3C20-44DA-808D-36F518F07891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87C7C7E-7432-4DE9-958C-61A8A2C62AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,12 +12,11 @@
     <sheet name="Resultados" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
   <si>
     <t>title</t>
   </si>
@@ -1244,9 +1243,6 @@
   </si>
   <si>
     <t>https://g1.globo.com/sp/santos-regiao/noticia/2023/12/31/retrospectiva-2023-confira-fotos-que-marcaram-o-ano-na-baixada-santista-vale-do-ribeira-sp.ghtml</t>
-  </si>
-  <si>
-    <t>[ERRO] Navigation timeout of 50000 ms exceeded</t>
   </si>
 </sst>
 </file>
@@ -1950,9 +1946,6 @@
       <c r="C4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
